--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
@@ -562,7 +562,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1444,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1635,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1700,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1830,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2086,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2395,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2521,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2586,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2651,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2777,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3147,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3334,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3399,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3464,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3590,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3960,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4025,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4090,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4399,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4586,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4773,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4899,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5025,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5090,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5277,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5342,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5529,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5594,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5659,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5846,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5972,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6159,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6224,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6350,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6415,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6480,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6545,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6671,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6858,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6923,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +6988,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7114,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7240,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7488,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7614,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7679,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7805,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7992,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8240,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8366,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8553,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8618,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8683,11 @@
           <t>77.601.267-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8748,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8813,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8939,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9126,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9191,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9317,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9382,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9508,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9634,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9760,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9886,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9951,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10016,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10081,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10146,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10272,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10398,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10463,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10711,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10959,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11085,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11394,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11459,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11524,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11589,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11715,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11780,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11967,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12032,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12158,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12345,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12471,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12658,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12723,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12788,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12975,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13040,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13227,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13292,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13357,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13422,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13487,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13613,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13739,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13804,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13869,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14056,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14121,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14186,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14434,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14621,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14747,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15117,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15182,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15430,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15617,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15804,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15869,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15934,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16060,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16186,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16251,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16377,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16442,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16507,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16572,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16820,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16885,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16950,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17015,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17080,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17694,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17942,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18068,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18194,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18259,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18446,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18511,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18576,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18946,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19072,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19259,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19568,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
@@ -5785,7 +5785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11211,7 +11215,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11906,7 +11914,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12410,7 +12422,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/sep-2026.xlsx
@@ -4432,7 +4432,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
